--- a/Data/Data_Exp_2.xlsx
+++ b/Data/Data_Exp_2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jandr\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3278A41-4699-43E9-A4A2-BC059B832033}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94130E16-0DD7-4858-AB45-1179075BE613}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" activeTab="2" xr2:uid="{9D6F8BE9-69B3-4971-B6E9-E9EAB2521403}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{9D6F8BE9-69B3-4971-B6E9-E9EAB2521403}"/>
   </bookViews>
   <sheets>
     <sheet name="Size" sheetId="2" r:id="rId1"/>
@@ -76,15 +76,6 @@
     <t>Basal</t>
   </si>
   <si>
-    <t>Gradient</t>
-  </si>
-  <si>
-    <t>Low_to_High</t>
-  </si>
-  <si>
-    <t>High_to_Low</t>
-  </si>
-  <si>
     <t>Time_s</t>
   </si>
   <si>
@@ -92,6 +83,15 @@
   </si>
   <si>
     <t>Temperature_°C</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Ascending</t>
+  </si>
+  <si>
+    <t>Descending</t>
   </si>
 </sst>
 </file>
@@ -137,7 +137,7 @@
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -747,7 +747,7 @@
         <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -755,7 +755,7 @@
         <v>5</v>
       </c>
       <c r="B2" s="1">
-        <v>3012</v>
+        <v>3010</v>
       </c>
       <c r="C2" s="1">
         <v>16</v>
@@ -764,7 +764,7 @@
         <v>62</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -772,7 +772,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="1">
-        <v>3012</v>
+        <v>3010</v>
       </c>
       <c r="C3" s="1">
         <v>17</v>
@@ -781,7 +781,7 @@
         <v>64</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -789,7 +789,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="1">
-        <v>3012</v>
+        <v>3010</v>
       </c>
       <c r="C4" s="1">
         <v>18</v>
@@ -798,7 +798,7 @@
         <v>70</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -806,7 +806,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="1">
-        <v>3012</v>
+        <v>3010</v>
       </c>
       <c r="C5" s="1">
         <v>19</v>
@@ -815,7 +815,7 @@
         <v>60</v>
       </c>
       <c r="E5" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -823,7 +823,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="1">
-        <v>3012</v>
+        <v>3010</v>
       </c>
       <c r="C6" s="1">
         <v>20</v>
@@ -832,7 +832,7 @@
         <v>68</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -840,7 +840,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1">
-        <v>3012</v>
+        <v>3010</v>
       </c>
       <c r="C7" s="1">
         <v>21</v>
@@ -849,7 +849,7 @@
         <v>54</v>
       </c>
       <c r="E7" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -857,7 +857,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="1">
-        <v>3012</v>
+        <v>3010</v>
       </c>
       <c r="C8" s="1">
         <v>23</v>
@@ -866,7 +866,7 @@
         <v>70</v>
       </c>
       <c r="E8" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -874,7 +874,7 @@
         <v>5</v>
       </c>
       <c r="B9" s="1">
-        <v>3012</v>
+        <v>3010</v>
       </c>
       <c r="C9" s="1">
         <v>25</v>
@@ -883,7 +883,7 @@
         <v>58</v>
       </c>
       <c r="E9" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -891,7 +891,7 @@
         <v>5</v>
       </c>
       <c r="B10" s="1">
-        <v>3012</v>
+        <v>3010</v>
       </c>
       <c r="C10" s="1">
         <v>26</v>
@@ -900,7 +900,7 @@
         <v>60</v>
       </c>
       <c r="E10" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -908,7 +908,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="1">
-        <v>3012</v>
+        <v>3010</v>
       </c>
       <c r="C11" s="1">
         <v>28</v>
@@ -917,7 +917,7 @@
         <v>68</v>
       </c>
       <c r="E11" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -925,7 +925,7 @@
         <v>5</v>
       </c>
       <c r="B12" s="1">
-        <v>3012</v>
+        <v>3010</v>
       </c>
       <c r="C12" s="1">
         <v>29</v>
@@ -934,7 +934,7 @@
         <v>68</v>
       </c>
       <c r="E12" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -942,7 +942,7 @@
         <v>5</v>
       </c>
       <c r="B13" s="1">
-        <v>3012</v>
+        <v>3010</v>
       </c>
       <c r="C13" s="1">
         <v>30</v>
@@ -951,7 +951,7 @@
         <v>68</v>
       </c>
       <c r="E13" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -959,7 +959,7 @@
         <v>6</v>
       </c>
       <c r="B14" s="1">
-        <v>2100</v>
+        <v>2300</v>
       </c>
       <c r="C14" s="1">
         <v>16</v>
@@ -968,7 +968,7 @@
         <v>60</v>
       </c>
       <c r="E14" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
@@ -976,7 +976,7 @@
         <v>6</v>
       </c>
       <c r="B15" s="1">
-        <v>2100</v>
+        <v>2300</v>
       </c>
       <c r="C15" s="1">
         <v>17</v>
@@ -985,7 +985,7 @@
         <v>74</v>
       </c>
       <c r="E15" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -993,7 +993,7 @@
         <v>6</v>
       </c>
       <c r="B16" s="1">
-        <v>2100</v>
+        <v>2300</v>
       </c>
       <c r="C16" s="1">
         <v>18</v>
@@ -1002,7 +1002,7 @@
         <v>70</v>
       </c>
       <c r="E16" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
@@ -1010,7 +1010,7 @@
         <v>6</v>
       </c>
       <c r="B17" s="1">
-        <v>2100</v>
+        <v>2300</v>
       </c>
       <c r="C17" s="1">
         <v>19</v>
@@ -1019,7 +1019,7 @@
         <v>50</v>
       </c>
       <c r="E17" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
@@ -1027,7 +1027,7 @@
         <v>6</v>
       </c>
       <c r="B18" s="1">
-        <v>2100</v>
+        <v>2300</v>
       </c>
       <c r="C18" s="1">
         <v>20</v>
@@ -1036,7 +1036,7 @@
         <v>64</v>
       </c>
       <c r="E18" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
@@ -1044,7 +1044,7 @@
         <v>6</v>
       </c>
       <c r="B19" s="1">
-        <v>2100</v>
+        <v>2300</v>
       </c>
       <c r="C19" s="1">
         <v>21</v>
@@ -1053,7 +1053,7 @@
         <v>64</v>
       </c>
       <c r="E19" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
@@ -1061,7 +1061,7 @@
         <v>6</v>
       </c>
       <c r="B20" s="1">
-        <v>2100</v>
+        <v>2300</v>
       </c>
       <c r="C20" s="1">
         <v>22</v>
@@ -1070,7 +1070,7 @@
         <v>60</v>
       </c>
       <c r="E20" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
@@ -1078,7 +1078,7 @@
         <v>6</v>
       </c>
       <c r="B21" s="1">
-        <v>2100</v>
+        <v>2300</v>
       </c>
       <c r="C21" s="1">
         <v>23</v>
@@ -1087,7 +1087,7 @@
         <v>54</v>
       </c>
       <c r="E21" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
@@ -1095,7 +1095,7 @@
         <v>6</v>
       </c>
       <c r="B22" s="1">
-        <v>2100</v>
+        <v>2300</v>
       </c>
       <c r="C22" s="1">
         <v>25</v>
@@ -1104,7 +1104,7 @@
         <v>64</v>
       </c>
       <c r="E22" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
@@ -1112,7 +1112,7 @@
         <v>6</v>
       </c>
       <c r="B23" s="1">
-        <v>2100</v>
+        <v>2300</v>
       </c>
       <c r="C23" s="1">
         <v>26</v>
@@ -1121,7 +1121,7 @@
         <v>72</v>
       </c>
       <c r="E23" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
@@ -1129,7 +1129,7 @@
         <v>6</v>
       </c>
       <c r="B24" s="1">
-        <v>2100</v>
+        <v>2300</v>
       </c>
       <c r="C24" s="1">
         <v>28</v>
@@ -1138,7 +1138,7 @@
         <v>66</v>
       </c>
       <c r="E24" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
@@ -1146,7 +1146,7 @@
         <v>6</v>
       </c>
       <c r="B25" s="1">
-        <v>2100</v>
+        <v>2300</v>
       </c>
       <c r="C25" s="1">
         <v>29</v>
@@ -1155,7 +1155,7 @@
         <v>66</v>
       </c>
       <c r="E25" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
@@ -1163,7 +1163,7 @@
         <v>6</v>
       </c>
       <c r="B26" s="1">
-        <v>2100</v>
+        <v>2300</v>
       </c>
       <c r="C26" s="1">
         <v>30</v>
@@ -1172,7 +1172,7 @@
         <v>74</v>
       </c>
       <c r="E26" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
@@ -1180,7 +1180,7 @@
         <v>7</v>
       </c>
       <c r="B27" s="1">
-        <v>1200</v>
+        <v>1560</v>
       </c>
       <c r="C27" s="1">
         <v>16</v>
@@ -1189,7 +1189,7 @@
         <v>72</v>
       </c>
       <c r="E27" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
@@ -1197,7 +1197,7 @@
         <v>7</v>
       </c>
       <c r="B28" s="1">
-        <v>1200</v>
+        <v>1560</v>
       </c>
       <c r="C28" s="1">
         <v>17</v>
@@ -1206,7 +1206,7 @@
         <v>78</v>
       </c>
       <c r="E28" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
@@ -1214,7 +1214,7 @@
         <v>7</v>
       </c>
       <c r="B29" s="1">
-        <v>1200</v>
+        <v>1560</v>
       </c>
       <c r="C29" s="1">
         <v>18</v>
@@ -1223,7 +1223,7 @@
         <v>80</v>
       </c>
       <c r="E29" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
@@ -1231,7 +1231,7 @@
         <v>7</v>
       </c>
       <c r="B30" s="1">
-        <v>1200</v>
+        <v>1560</v>
       </c>
       <c r="C30" s="1">
         <v>19</v>
@@ -1240,7 +1240,7 @@
         <v>60</v>
       </c>
       <c r="E30" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
@@ -1248,7 +1248,7 @@
         <v>7</v>
       </c>
       <c r="B31" s="1">
-        <v>1200</v>
+        <v>1560</v>
       </c>
       <c r="C31" s="1">
         <v>20</v>
@@ -1257,7 +1257,7 @@
         <v>70</v>
       </c>
       <c r="E31" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
@@ -1265,7 +1265,7 @@
         <v>7</v>
       </c>
       <c r="B32" s="1">
-        <v>1200</v>
+        <v>1560</v>
       </c>
       <c r="C32" s="1">
         <v>21</v>
@@ -1274,7 +1274,7 @@
         <v>74</v>
       </c>
       <c r="E32" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
@@ -1282,7 +1282,7 @@
         <v>7</v>
       </c>
       <c r="B33" s="1">
-        <v>1200</v>
+        <v>1560</v>
       </c>
       <c r="C33" s="1">
         <v>22</v>
@@ -1291,7 +1291,7 @@
         <v>72</v>
       </c>
       <c r="E33" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
@@ -1299,7 +1299,7 @@
         <v>7</v>
       </c>
       <c r="B34" s="1">
-        <v>1200</v>
+        <v>1560</v>
       </c>
       <c r="C34" s="1">
         <v>23</v>
@@ -1308,7 +1308,7 @@
         <v>70</v>
       </c>
       <c r="E34" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
@@ -1316,7 +1316,7 @@
         <v>7</v>
       </c>
       <c r="B35" s="1">
-        <v>1200</v>
+        <v>1560</v>
       </c>
       <c r="C35" s="1">
         <v>25</v>
@@ -1325,7 +1325,7 @@
         <v>76</v>
       </c>
       <c r="E35" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
@@ -1333,7 +1333,7 @@
         <v>7</v>
       </c>
       <c r="B36" s="1">
-        <v>1200</v>
+        <v>1560</v>
       </c>
       <c r="C36" s="1">
         <v>26</v>
@@ -1342,7 +1342,7 @@
         <v>72</v>
       </c>
       <c r="E36" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
@@ -1350,7 +1350,7 @@
         <v>7</v>
       </c>
       <c r="B37" s="1">
-        <v>1200</v>
+        <v>1560</v>
       </c>
       <c r="C37" s="1">
         <v>27</v>
@@ -1359,7 +1359,7 @@
         <v>78</v>
       </c>
       <c r="E37" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
@@ -1367,7 +1367,7 @@
         <v>7</v>
       </c>
       <c r="B38" s="1">
-        <v>1200</v>
+        <v>1560</v>
       </c>
       <c r="C38" s="1">
         <v>28</v>
@@ -1376,7 +1376,7 @@
         <v>84</v>
       </c>
       <c r="E38" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
@@ -1384,7 +1384,7 @@
         <v>7</v>
       </c>
       <c r="B39" s="1">
-        <v>1200</v>
+        <v>1560</v>
       </c>
       <c r="C39" s="1">
         <v>30</v>
@@ -1393,7 +1393,7 @@
         <v>90</v>
       </c>
       <c r="E39" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
@@ -1401,7 +1401,7 @@
         <v>8</v>
       </c>
       <c r="B40" s="1">
-        <v>919</v>
+        <v>910</v>
       </c>
       <c r="C40" s="1">
         <v>16</v>
@@ -1410,7 +1410,7 @@
         <v>66</v>
       </c>
       <c r="E40" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
@@ -1418,7 +1418,7 @@
         <v>8</v>
       </c>
       <c r="B41" s="1">
-        <v>919</v>
+        <v>910</v>
       </c>
       <c r="C41" s="1">
         <v>17</v>
@@ -1427,7 +1427,7 @@
         <v>80</v>
       </c>
       <c r="E41" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
@@ -1435,7 +1435,7 @@
         <v>8</v>
       </c>
       <c r="B42" s="1">
-        <v>919</v>
+        <v>910</v>
       </c>
       <c r="C42" s="1">
         <v>18</v>
@@ -1444,7 +1444,7 @@
         <v>84</v>
       </c>
       <c r="E42" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
@@ -1452,7 +1452,7 @@
         <v>8</v>
       </c>
       <c r="B43" s="1">
-        <v>919</v>
+        <v>910</v>
       </c>
       <c r="C43" s="1">
         <v>19</v>
@@ -1461,7 +1461,7 @@
         <v>72</v>
       </c>
       <c r="E43" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
@@ -1469,7 +1469,7 @@
         <v>8</v>
       </c>
       <c r="B44" s="1">
-        <v>919</v>
+        <v>910</v>
       </c>
       <c r="C44" s="1">
         <v>20</v>
@@ -1478,7 +1478,7 @@
         <v>66</v>
       </c>
       <c r="E44" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
@@ -1486,7 +1486,7 @@
         <v>8</v>
       </c>
       <c r="B45" s="1">
-        <v>919</v>
+        <v>910</v>
       </c>
       <c r="C45" s="1">
         <v>22</v>
@@ -1495,7 +1495,7 @@
         <v>80</v>
       </c>
       <c r="E45" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
@@ -1503,7 +1503,7 @@
         <v>8</v>
       </c>
       <c r="B46" s="1">
-        <v>919</v>
+        <v>910</v>
       </c>
       <c r="C46" s="1">
         <v>23</v>
@@ -1512,7 +1512,7 @@
         <v>78</v>
       </c>
       <c r="E46" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
@@ -1520,7 +1520,7 @@
         <v>8</v>
       </c>
       <c r="B47" s="1">
-        <v>919</v>
+        <v>910</v>
       </c>
       <c r="C47" s="1">
         <v>25</v>
@@ -1529,7 +1529,7 @@
         <v>80</v>
       </c>
       <c r="E47" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
@@ -1537,7 +1537,7 @@
         <v>8</v>
       </c>
       <c r="B48" s="1">
-        <v>919</v>
+        <v>910</v>
       </c>
       <c r="C48" s="1">
         <v>26</v>
@@ -1546,7 +1546,7 @@
         <v>90</v>
       </c>
       <c r="E48" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
@@ -1554,7 +1554,7 @@
         <v>8</v>
       </c>
       <c r="B49" s="1">
-        <v>919</v>
+        <v>910</v>
       </c>
       <c r="C49" s="1">
         <v>27</v>
@@ -1563,7 +1563,7 @@
         <v>68</v>
       </c>
       <c r="E49" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
@@ -1571,7 +1571,7 @@
         <v>8</v>
       </c>
       <c r="B50" s="1">
-        <v>919</v>
+        <v>910</v>
       </c>
       <c r="C50" s="1">
         <v>28</v>
@@ -1580,7 +1580,7 @@
         <v>88</v>
       </c>
       <c r="E50" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
@@ -1588,7 +1588,7 @@
         <v>8</v>
       </c>
       <c r="B51" s="1">
-        <v>919</v>
+        <v>910</v>
       </c>
       <c r="C51" s="1">
         <v>29</v>
@@ -1597,7 +1597,7 @@
         <v>92</v>
       </c>
       <c r="E51" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
@@ -1605,7 +1605,7 @@
         <v>8</v>
       </c>
       <c r="B52" s="1">
-        <v>919</v>
+        <v>910</v>
       </c>
       <c r="C52" s="1">
         <v>30</v>
@@ -1614,7 +1614,7 @@
         <v>96</v>
       </c>
       <c r="E52" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
@@ -1622,7 +1622,7 @@
         <v>9</v>
       </c>
       <c r="B53" s="1">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="C53" s="1">
         <v>16</v>
@@ -1631,7 +1631,7 @@
         <v>62</v>
       </c>
       <c r="E53" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
@@ -1639,7 +1639,7 @@
         <v>9</v>
       </c>
       <c r="B54" s="1">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="C54" s="1">
         <v>17</v>
@@ -1648,7 +1648,7 @@
         <v>66</v>
       </c>
       <c r="E54" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
@@ -1656,7 +1656,7 @@
         <v>9</v>
       </c>
       <c r="B55" s="1">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="C55" s="1">
         <v>18</v>
@@ -1665,7 +1665,7 @@
         <v>90</v>
       </c>
       <c r="E55" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
@@ -1673,7 +1673,7 @@
         <v>9</v>
       </c>
       <c r="B56" s="1">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="C56" s="1">
         <v>21</v>
@@ -1682,7 +1682,7 @@
         <v>72</v>
       </c>
       <c r="E56" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
@@ -1690,7 +1690,7 @@
         <v>9</v>
       </c>
       <c r="B57" s="1">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="C57" s="1">
         <v>23</v>
@@ -1699,7 +1699,7 @@
         <v>70</v>
       </c>
       <c r="E57" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
@@ -1707,7 +1707,7 @@
         <v>9</v>
       </c>
       <c r="B58" s="1">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="C58" s="1">
         <v>24</v>
@@ -1716,7 +1716,7 @@
         <v>86</v>
       </c>
       <c r="E58" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
@@ -1724,7 +1724,7 @@
         <v>9</v>
       </c>
       <c r="B59" s="1">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="C59" s="1">
         <v>25</v>
@@ -1733,7 +1733,7 @@
         <v>72</v>
       </c>
       <c r="E59" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
@@ -1741,7 +1741,7 @@
         <v>10</v>
       </c>
       <c r="B60" s="1">
-        <v>2620</v>
+        <v>2560</v>
       </c>
       <c r="C60" s="1">
         <v>16</v>
@@ -1750,7 +1750,7 @@
         <v>50</v>
       </c>
       <c r="E60" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
@@ -1758,7 +1758,7 @@
         <v>10</v>
       </c>
       <c r="B61" s="1">
-        <v>2620</v>
+        <v>2560</v>
       </c>
       <c r="C61" s="1">
         <v>17</v>
@@ -1767,7 +1767,7 @@
         <v>64</v>
       </c>
       <c r="E61" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
@@ -1775,7 +1775,7 @@
         <v>10</v>
       </c>
       <c r="B62" s="1">
-        <v>2620</v>
+        <v>2560</v>
       </c>
       <c r="C62" s="1">
         <v>18</v>
@@ -1784,7 +1784,7 @@
         <v>66</v>
       </c>
       <c r="E62" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
@@ -1792,7 +1792,7 @@
         <v>10</v>
       </c>
       <c r="B63" s="1">
-        <v>2620</v>
+        <v>2560</v>
       </c>
       <c r="C63" s="1">
         <v>19</v>
@@ -1801,7 +1801,7 @@
         <v>46</v>
       </c>
       <c r="E63" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
@@ -1809,7 +1809,7 @@
         <v>10</v>
       </c>
       <c r="B64" s="1">
-        <v>2620</v>
+        <v>2560</v>
       </c>
       <c r="C64" s="1">
         <v>20</v>
@@ -1818,7 +1818,7 @@
         <v>46</v>
       </c>
       <c r="E64" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
@@ -1826,7 +1826,7 @@
         <v>10</v>
       </c>
       <c r="B65" s="1">
-        <v>2620</v>
+        <v>2560</v>
       </c>
       <c r="C65" s="1">
         <v>21</v>
@@ -1835,7 +1835,7 @@
         <v>46</v>
       </c>
       <c r="E65" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
@@ -1843,7 +1843,7 @@
         <v>10</v>
       </c>
       <c r="B66" s="1">
-        <v>2620</v>
+        <v>2560</v>
       </c>
       <c r="C66" s="1">
         <v>22</v>
@@ -1852,7 +1852,7 @@
         <v>60</v>
       </c>
       <c r="E66" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
@@ -1860,7 +1860,7 @@
         <v>10</v>
       </c>
       <c r="B67" s="1">
-        <v>2620</v>
+        <v>2560</v>
       </c>
       <c r="C67" s="1">
         <v>23</v>
@@ -1869,7 +1869,7 @@
         <v>48</v>
       </c>
       <c r="E67" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
@@ -1877,7 +1877,7 @@
         <v>10</v>
       </c>
       <c r="B68" s="1">
-        <v>2620</v>
+        <v>2560</v>
       </c>
       <c r="C68" s="1">
         <v>24</v>
@@ -1886,7 +1886,7 @@
         <v>64</v>
       </c>
       <c r="E68" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
@@ -1894,7 +1894,7 @@
         <v>10</v>
       </c>
       <c r="B69" s="1">
-        <v>2620</v>
+        <v>2560</v>
       </c>
       <c r="C69" s="1">
         <v>25</v>
@@ -1903,7 +1903,7 @@
         <v>48</v>
       </c>
       <c r="E69" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
@@ -1911,7 +1911,7 @@
         <v>10</v>
       </c>
       <c r="B70" s="1">
-        <v>2620</v>
+        <v>2560</v>
       </c>
       <c r="C70" s="1">
         <v>26</v>
@@ -1920,7 +1920,7 @@
         <v>60</v>
       </c>
       <c r="E70" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
@@ -1928,7 +1928,7 @@
         <v>10</v>
       </c>
       <c r="B71" s="1">
-        <v>2620</v>
+        <v>2560</v>
       </c>
       <c r="C71" s="1">
         <v>27</v>
@@ -1937,7 +1937,7 @@
         <v>66</v>
       </c>
       <c r="E71" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
@@ -1945,7 +1945,7 @@
         <v>10</v>
       </c>
       <c r="B72" s="1">
-        <v>2620</v>
+        <v>2560</v>
       </c>
       <c r="C72" s="1">
         <v>28</v>
@@ -1954,7 +1954,7 @@
         <v>62</v>
       </c>
       <c r="E72" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
@@ -1962,7 +1962,7 @@
         <v>10</v>
       </c>
       <c r="B73" s="1">
-        <v>2620</v>
+        <v>2560</v>
       </c>
       <c r="C73" s="1">
         <v>29</v>
@@ -1971,7 +1971,7 @@
         <v>60</v>
       </c>
       <c r="E73" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.3">
@@ -1979,7 +1979,7 @@
         <v>10</v>
       </c>
       <c r="B74" s="1">
-        <v>2620</v>
+        <v>2560</v>
       </c>
       <c r="C74" s="1">
         <v>30</v>
@@ -1988,7 +1988,7 @@
         <v>60</v>
       </c>
       <c r="E74" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.3">
@@ -1996,7 +1996,7 @@
         <v>5</v>
       </c>
       <c r="B75" s="1">
-        <v>3012</v>
+        <v>3010</v>
       </c>
       <c r="C75" s="1">
         <v>1</v>
@@ -2005,7 +2005,7 @@
         <v>38</v>
       </c>
       <c r="E75" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">
@@ -2013,7 +2013,7 @@
         <v>5</v>
       </c>
       <c r="B76" s="1">
-        <v>3012</v>
+        <v>3010</v>
       </c>
       <c r="C76" s="1">
         <v>2</v>
@@ -2022,7 +2022,7 @@
         <v>30</v>
       </c>
       <c r="E76" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.3">
@@ -2030,7 +2030,7 @@
         <v>5</v>
       </c>
       <c r="B77" s="1">
-        <v>3012</v>
+        <v>3010</v>
       </c>
       <c r="C77" s="1">
         <v>4</v>
@@ -2039,7 +2039,7 @@
         <v>30</v>
       </c>
       <c r="E77" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">
@@ -2047,7 +2047,7 @@
         <v>5</v>
       </c>
       <c r="B78" s="1">
-        <v>3012</v>
+        <v>3010</v>
       </c>
       <c r="C78" s="1">
         <v>5</v>
@@ -2056,7 +2056,7 @@
         <v>32</v>
       </c>
       <c r="E78" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.3">
@@ -2064,7 +2064,7 @@
         <v>5</v>
       </c>
       <c r="B79" s="1">
-        <v>3012</v>
+        <v>3010</v>
       </c>
       <c r="C79" s="1">
         <v>6</v>
@@ -2073,7 +2073,7 @@
         <v>38</v>
       </c>
       <c r="E79" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.3">
@@ -2081,7 +2081,7 @@
         <v>5</v>
       </c>
       <c r="B80" s="1">
-        <v>3012</v>
+        <v>3010</v>
       </c>
       <c r="C80" s="1">
         <v>7</v>
@@ -2090,7 +2090,7 @@
         <v>28</v>
       </c>
       <c r="E80" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.3">
@@ -2098,7 +2098,7 @@
         <v>5</v>
       </c>
       <c r="B81" s="1">
-        <v>3012</v>
+        <v>3010</v>
       </c>
       <c r="C81" s="1">
         <v>8</v>
@@ -2107,7 +2107,7 @@
         <v>28</v>
       </c>
       <c r="E81" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.3">
@@ -2115,7 +2115,7 @@
         <v>5</v>
       </c>
       <c r="B82" s="1">
-        <v>3012</v>
+        <v>3010</v>
       </c>
       <c r="C82" s="1">
         <v>10</v>
@@ -2124,7 +2124,7 @@
         <v>34</v>
       </c>
       <c r="E82" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
@@ -2132,7 +2132,7 @@
         <v>5</v>
       </c>
       <c r="B83" s="1">
-        <v>3012</v>
+        <v>3010</v>
       </c>
       <c r="C83" s="1">
         <v>11</v>
@@ -2141,7 +2141,7 @@
         <v>36</v>
       </c>
       <c r="E83" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.3">
@@ -2149,7 +2149,7 @@
         <v>5</v>
       </c>
       <c r="B84" s="1">
-        <v>3012</v>
+        <v>3010</v>
       </c>
       <c r="C84" s="1">
         <v>12</v>
@@ -2158,7 +2158,7 @@
         <v>32</v>
       </c>
       <c r="E84" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.3">
@@ -2166,7 +2166,7 @@
         <v>5</v>
       </c>
       <c r="B85" s="1">
-        <v>3012</v>
+        <v>3010</v>
       </c>
       <c r="C85" s="1">
         <v>13</v>
@@ -2175,7 +2175,7 @@
         <v>24</v>
       </c>
       <c r="E85" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
@@ -2183,7 +2183,7 @@
         <v>5</v>
       </c>
       <c r="B86" s="1">
-        <v>3012</v>
+        <v>3010</v>
       </c>
       <c r="C86" s="1">
         <v>14</v>
@@ -2192,7 +2192,7 @@
         <v>33</v>
       </c>
       <c r="E86" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.3">
@@ -2200,7 +2200,7 @@
         <v>5</v>
       </c>
       <c r="B87" s="1">
-        <v>3012</v>
+        <v>3010</v>
       </c>
       <c r="C87" s="1">
         <v>15</v>
@@ -2209,7 +2209,7 @@
         <v>30</v>
       </c>
       <c r="E87" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
@@ -2217,7 +2217,7 @@
         <v>6</v>
       </c>
       <c r="B88" s="1">
-        <v>2100</v>
+        <v>2300</v>
       </c>
       <c r="C88" s="1">
         <v>1</v>
@@ -2226,7 +2226,7 @@
         <v>64</v>
       </c>
       <c r="E88" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.3">
@@ -2234,7 +2234,7 @@
         <v>6</v>
       </c>
       <c r="B89" s="1">
-        <v>2100</v>
+        <v>2300</v>
       </c>
       <c r="C89" s="1">
         <v>2</v>
@@ -2243,7 +2243,7 @@
         <v>56</v>
       </c>
       <c r="E89" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.3">
@@ -2251,7 +2251,7 @@
         <v>6</v>
       </c>
       <c r="B90" s="1">
-        <v>2100</v>
+        <v>2300</v>
       </c>
       <c r="C90" s="1">
         <v>3</v>
@@ -2260,7 +2260,7 @@
         <v>60</v>
       </c>
       <c r="E90" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.3">
@@ -2268,7 +2268,7 @@
         <v>6</v>
       </c>
       <c r="B91" s="1">
-        <v>2100</v>
+        <v>2300</v>
       </c>
       <c r="C91" s="1">
         <v>4</v>
@@ -2277,7 +2277,7 @@
         <v>50</v>
       </c>
       <c r="E91" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.3">
@@ -2285,7 +2285,7 @@
         <v>6</v>
       </c>
       <c r="B92" s="1">
-        <v>2100</v>
+        <v>2300</v>
       </c>
       <c r="C92" s="1">
         <v>5</v>
@@ -2294,7 +2294,7 @@
         <v>58</v>
       </c>
       <c r="E92" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
@@ -2302,7 +2302,7 @@
         <v>6</v>
       </c>
       <c r="B93" s="1">
-        <v>2100</v>
+        <v>2300</v>
       </c>
       <c r="C93" s="1">
         <v>6</v>
@@ -2311,7 +2311,7 @@
         <v>56</v>
       </c>
       <c r="E93" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.3">
@@ -2319,7 +2319,7 @@
         <v>6</v>
       </c>
       <c r="B94" s="1">
-        <v>2100</v>
+        <v>2300</v>
       </c>
       <c r="C94" s="1">
         <v>7</v>
@@ -2328,7 +2328,7 @@
         <v>60</v>
       </c>
       <c r="E94" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.3">
@@ -2336,7 +2336,7 @@
         <v>6</v>
       </c>
       <c r="B95" s="1">
-        <v>2100</v>
+        <v>2300</v>
       </c>
       <c r="C95" s="1">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>48</v>
       </c>
       <c r="E95" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.3">
@@ -2353,7 +2353,7 @@
         <v>6</v>
       </c>
       <c r="B96" s="1">
-        <v>2100</v>
+        <v>2300</v>
       </c>
       <c r="C96" s="1">
         <v>10</v>
@@ -2362,7 +2362,7 @@
         <v>46</v>
       </c>
       <c r="E96" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.3">
@@ -2370,7 +2370,7 @@
         <v>6</v>
       </c>
       <c r="B97" s="1">
-        <v>2100</v>
+        <v>2300</v>
       </c>
       <c r="C97" s="1">
         <v>11</v>
@@ -2379,7 +2379,7 @@
         <v>60</v>
       </c>
       <c r="E97" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.3">
@@ -2387,7 +2387,7 @@
         <v>6</v>
       </c>
       <c r="B98" s="1">
-        <v>2100</v>
+        <v>2300</v>
       </c>
       <c r="C98" s="1">
         <v>12</v>
@@ -2396,7 +2396,7 @@
         <v>58</v>
       </c>
       <c r="E98" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.3">
@@ -2404,7 +2404,7 @@
         <v>6</v>
       </c>
       <c r="B99" s="1">
-        <v>2100</v>
+        <v>2300</v>
       </c>
       <c r="C99" s="1">
         <v>13</v>
@@ -2413,7 +2413,7 @@
         <v>40</v>
       </c>
       <c r="E99" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.3">
@@ -2421,7 +2421,7 @@
         <v>6</v>
       </c>
       <c r="B100" s="1">
-        <v>2100</v>
+        <v>2300</v>
       </c>
       <c r="C100" s="1">
         <v>14</v>
@@ -2430,7 +2430,7 @@
         <v>52</v>
       </c>
       <c r="E100" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.3">
@@ -2438,7 +2438,7 @@
         <v>7</v>
       </c>
       <c r="B101" s="1">
-        <v>1200</v>
+        <v>1560</v>
       </c>
       <c r="C101" s="1">
         <v>1</v>
@@ -2447,7 +2447,7 @@
         <v>78</v>
       </c>
       <c r="E101" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.3">
@@ -2455,7 +2455,7 @@
         <v>7</v>
       </c>
       <c r="B102" s="1">
-        <v>1200</v>
+        <v>1560</v>
       </c>
       <c r="C102" s="1">
         <v>2</v>
@@ -2464,7 +2464,7 @@
         <v>58</v>
       </c>
       <c r="E102" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.3">
@@ -2472,7 +2472,7 @@
         <v>7</v>
       </c>
       <c r="B103" s="1">
-        <v>1200</v>
+        <v>1560</v>
       </c>
       <c r="C103" s="1">
         <v>3</v>
@@ -2481,7 +2481,7 @@
         <v>80</v>
       </c>
       <c r="E103" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.3">
@@ -2489,7 +2489,7 @@
         <v>7</v>
       </c>
       <c r="B104" s="1">
-        <v>1200</v>
+        <v>1560</v>
       </c>
       <c r="C104" s="1">
         <v>5</v>
@@ -2498,7 +2498,7 @@
         <v>74</v>
       </c>
       <c r="E104" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.3">
@@ -2506,7 +2506,7 @@
         <v>7</v>
       </c>
       <c r="B105" s="1">
-        <v>1200</v>
+        <v>1560</v>
       </c>
       <c r="C105" s="1">
         <v>6</v>
@@ -2515,7 +2515,7 @@
         <v>76</v>
       </c>
       <c r="E105" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.3">
@@ -2523,7 +2523,7 @@
         <v>7</v>
       </c>
       <c r="B106" s="1">
-        <v>1200</v>
+        <v>1560</v>
       </c>
       <c r="C106" s="1">
         <v>7</v>
@@ -2532,7 +2532,7 @@
         <v>68</v>
       </c>
       <c r="E106" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.3">
@@ -2540,7 +2540,7 @@
         <v>7</v>
       </c>
       <c r="B107" s="1">
-        <v>1200</v>
+        <v>1560</v>
       </c>
       <c r="C107" s="1">
         <v>8</v>
@@ -2549,7 +2549,7 @@
         <v>52</v>
       </c>
       <c r="E107" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.3">
@@ -2557,7 +2557,7 @@
         <v>7</v>
       </c>
       <c r="B108" s="1">
-        <v>1200</v>
+        <v>1560</v>
       </c>
       <c r="C108" s="1">
         <v>9</v>
@@ -2566,7 +2566,7 @@
         <v>90</v>
       </c>
       <c r="E108" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.3">
@@ -2574,7 +2574,7 @@
         <v>7</v>
       </c>
       <c r="B109" s="1">
-        <v>1200</v>
+        <v>1560</v>
       </c>
       <c r="C109" s="1">
         <v>10</v>
@@ -2583,7 +2583,7 @@
         <v>68</v>
       </c>
       <c r="E109" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.3">
@@ -2591,7 +2591,7 @@
         <v>7</v>
       </c>
       <c r="B110" s="1">
-        <v>1200</v>
+        <v>1560</v>
       </c>
       <c r="C110" s="1">
         <v>11</v>
@@ -2600,7 +2600,7 @@
         <v>62</v>
       </c>
       <c r="E110" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.3">
@@ -2608,7 +2608,7 @@
         <v>7</v>
       </c>
       <c r="B111" s="1">
-        <v>1200</v>
+        <v>1560</v>
       </c>
       <c r="C111" s="1">
         <v>13</v>
@@ -2617,7 +2617,7 @@
         <v>62</v>
       </c>
       <c r="E111" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.3">
@@ -2625,7 +2625,7 @@
         <v>7</v>
       </c>
       <c r="B112" s="1">
-        <v>1200</v>
+        <v>1560</v>
       </c>
       <c r="C112" s="1">
         <v>14</v>
@@ -2634,7 +2634,7 @@
         <v>66</v>
       </c>
       <c r="E112" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.3">
@@ -2642,7 +2642,7 @@
         <v>8</v>
       </c>
       <c r="B113" s="1">
-        <v>919</v>
+        <v>910</v>
       </c>
       <c r="C113" s="1">
         <v>1</v>
@@ -2651,7 +2651,7 @@
         <v>84</v>
       </c>
       <c r="E113" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.3">
@@ -2659,7 +2659,7 @@
         <v>8</v>
       </c>
       <c r="B114" s="1">
-        <v>919</v>
+        <v>910</v>
       </c>
       <c r="C114" s="1">
         <v>2</v>
@@ -2668,7 +2668,7 @@
         <v>70</v>
       </c>
       <c r="E114" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.3">
@@ -2676,7 +2676,7 @@
         <v>8</v>
       </c>
       <c r="B115" s="1">
-        <v>919</v>
+        <v>910</v>
       </c>
       <c r="C115" s="1">
         <v>3</v>
@@ -2685,7 +2685,7 @@
         <v>78</v>
       </c>
       <c r="E115" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.3">
@@ -2693,7 +2693,7 @@
         <v>8</v>
       </c>
       <c r="B116" s="1">
-        <v>919</v>
+        <v>910</v>
       </c>
       <c r="C116" s="1">
         <v>5</v>
@@ -2702,7 +2702,7 @@
         <v>86</v>
       </c>
       <c r="E116" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.3">
@@ -2710,7 +2710,7 @@
         <v>8</v>
       </c>
       <c r="B117" s="1">
-        <v>919</v>
+        <v>910</v>
       </c>
       <c r="C117" s="1">
         <v>7</v>
@@ -2719,7 +2719,7 @@
         <v>90</v>
       </c>
       <c r="E117" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.3">
@@ -2727,7 +2727,7 @@
         <v>8</v>
       </c>
       <c r="B118" s="1">
-        <v>919</v>
+        <v>910</v>
       </c>
       <c r="C118" s="1">
         <v>8</v>
@@ -2736,7 +2736,7 @@
         <v>68</v>
       </c>
       <c r="E118" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.3">
@@ -2744,7 +2744,7 @@
         <v>8</v>
       </c>
       <c r="B119" s="1">
-        <v>919</v>
+        <v>910</v>
       </c>
       <c r="C119" s="1">
         <v>9</v>
@@ -2753,7 +2753,7 @@
         <v>100</v>
       </c>
       <c r="E119" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.3">
@@ -2761,7 +2761,7 @@
         <v>9</v>
       </c>
       <c r="B120" s="1">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="C120" s="1">
         <v>3</v>
@@ -2770,7 +2770,7 @@
         <v>94</v>
       </c>
       <c r="E120" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.3">
@@ -2778,7 +2778,7 @@
         <v>9</v>
       </c>
       <c r="B121" s="1">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="C121" s="1">
         <v>5</v>
@@ -2787,7 +2787,7 @@
         <v>82</v>
       </c>
       <c r="E121" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.3">
@@ -2795,7 +2795,7 @@
         <v>9</v>
       </c>
       <c r="B122" s="1">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="C122" s="1">
         <v>6</v>
@@ -2804,7 +2804,7 @@
         <v>90</v>
       </c>
       <c r="E122" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.3">
@@ -2812,7 +2812,7 @@
         <v>9</v>
       </c>
       <c r="B123" s="1">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="C123" s="1">
         <v>7</v>
@@ -2821,7 +2821,7 @@
         <v>66</v>
       </c>
       <c r="E123" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.3">
@@ -2829,7 +2829,7 @@
         <v>9</v>
       </c>
       <c r="B124" s="1">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="C124" s="1">
         <v>8</v>
@@ -2838,7 +2838,7 @@
         <v>62</v>
       </c>
       <c r="E124" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.3">
@@ -2846,7 +2846,7 @@
         <v>9</v>
       </c>
       <c r="B125" s="1">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="C125" s="1">
         <v>9</v>
@@ -2855,7 +2855,7 @@
         <v>106</v>
       </c>
       <c r="E125" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.3">
@@ -2863,7 +2863,7 @@
         <v>9</v>
       </c>
       <c r="B126" s="1">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="C126" s="1">
         <v>10</v>
@@ -2872,7 +2872,7 @@
         <v>74</v>
       </c>
       <c r="E126" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.3">
@@ -2880,7 +2880,7 @@
         <v>9</v>
       </c>
       <c r="B127" s="1">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="C127" s="1">
         <v>13</v>
@@ -2889,7 +2889,7 @@
         <v>60</v>
       </c>
       <c r="E127" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.3">
@@ -2897,7 +2897,7 @@
         <v>9</v>
       </c>
       <c r="B128" s="1">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="C128" s="1">
         <v>14</v>
@@ -2906,7 +2906,7 @@
         <v>70</v>
       </c>
       <c r="E128" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.3">
@@ -2914,7 +2914,7 @@
         <v>10</v>
       </c>
       <c r="B129" s="1">
-        <v>2620</v>
+        <v>2560</v>
       </c>
       <c r="C129" s="1">
         <v>1</v>
@@ -2923,7 +2923,7 @@
         <v>56</v>
       </c>
       <c r="E129" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.3">
@@ -2931,7 +2931,7 @@
         <v>10</v>
       </c>
       <c r="B130" s="1">
-        <v>2620</v>
+        <v>2560</v>
       </c>
       <c r="C130" s="1">
         <v>2</v>
@@ -2940,7 +2940,7 @@
         <v>42</v>
       </c>
       <c r="E130" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.3">
@@ -2948,7 +2948,7 @@
         <v>10</v>
       </c>
       <c r="B131" s="1">
-        <v>2620</v>
+        <v>2560</v>
       </c>
       <c r="C131" s="1">
         <v>3</v>
@@ -2957,7 +2957,7 @@
         <v>56</v>
       </c>
       <c r="E131" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.3">
@@ -2965,7 +2965,7 @@
         <v>10</v>
       </c>
       <c r="B132" s="1">
-        <v>2620</v>
+        <v>2560</v>
       </c>
       <c r="C132" s="1">
         <v>4</v>
@@ -2974,7 +2974,7 @@
         <v>58</v>
       </c>
       <c r="E132" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.3">
@@ -2982,7 +2982,7 @@
         <v>10</v>
       </c>
       <c r="B133" s="1">
-        <v>2620</v>
+        <v>2560</v>
       </c>
       <c r="C133" s="1">
         <v>5</v>
@@ -2991,7 +2991,7 @@
         <v>50</v>
       </c>
       <c r="E133" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.3">
@@ -2999,7 +2999,7 @@
         <v>10</v>
       </c>
       <c r="B134" s="1">
-        <v>2620</v>
+        <v>2560</v>
       </c>
       <c r="C134" s="1">
         <v>6</v>
@@ -3008,7 +3008,7 @@
         <v>64</v>
       </c>
       <c r="E134" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.3">
@@ -3016,7 +3016,7 @@
         <v>10</v>
       </c>
       <c r="B135" s="1">
-        <v>2620</v>
+        <v>2560</v>
       </c>
       <c r="C135" s="1">
         <v>7</v>
@@ -3025,7 +3025,7 @@
         <v>50</v>
       </c>
       <c r="E135" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.3">
@@ -3033,7 +3033,7 @@
         <v>10</v>
       </c>
       <c r="B136" s="1">
-        <v>2620</v>
+        <v>2560</v>
       </c>
       <c r="C136" s="1">
         <v>8</v>
@@ -3042,7 +3042,7 @@
         <v>46</v>
       </c>
       <c r="E136" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.3">
@@ -3050,7 +3050,7 @@
         <v>10</v>
       </c>
       <c r="B137" s="1">
-        <v>2620</v>
+        <v>2560</v>
       </c>
       <c r="C137" s="1">
         <v>9</v>
@@ -3059,7 +3059,7 @@
         <v>58</v>
       </c>
       <c r="E137" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.3">
@@ -3067,7 +3067,7 @@
         <v>10</v>
       </c>
       <c r="B138" s="1">
-        <v>2620</v>
+        <v>2560</v>
       </c>
       <c r="C138" s="1">
         <v>10</v>
@@ -3076,7 +3076,7 @@
         <v>60</v>
       </c>
       <c r="E138" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.3">
@@ -3084,7 +3084,7 @@
         <v>10</v>
       </c>
       <c r="B139" s="1">
-        <v>2620</v>
+        <v>2560</v>
       </c>
       <c r="C139" s="1">
         <v>11</v>
@@ -3093,7 +3093,7 @@
         <v>60</v>
       </c>
       <c r="E139" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.3">
@@ -3101,7 +3101,7 @@
         <v>10</v>
       </c>
       <c r="B140" s="1">
-        <v>2620</v>
+        <v>2560</v>
       </c>
       <c r="C140" s="1">
         <v>12</v>
@@ -3110,7 +3110,7 @@
         <v>54</v>
       </c>
       <c r="E140" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.3">
@@ -3118,7 +3118,7 @@
         <v>10</v>
       </c>
       <c r="B141" s="1">
-        <v>2620</v>
+        <v>2560</v>
       </c>
       <c r="C141" s="1">
         <v>13</v>
@@ -3127,7 +3127,7 @@
         <v>52</v>
       </c>
       <c r="E141" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.3">
@@ -3135,7 +3135,7 @@
         <v>10</v>
       </c>
       <c r="B142" s="1">
-        <v>2620</v>
+        <v>2560</v>
       </c>
       <c r="C142" s="1">
         <v>14</v>
@@ -3144,7 +3144,7 @@
         <v>42</v>
       </c>
       <c r="E142" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.3">
@@ -3152,7 +3152,7 @@
         <v>10</v>
       </c>
       <c r="B143" s="1">
-        <v>2620</v>
+        <v>2560</v>
       </c>
       <c r="C143" s="1">
         <v>15</v>
@@ -3161,7 +3161,7 @@
         <v>66</v>
       </c>
       <c r="E143" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -3180,13 +3180,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
